--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135784660</v>
+        <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412209</v>
+        <v>412178</v>
       </c>
       <c r="R2" t="n">
-        <v>6967343</v>
+        <v>6967169</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +765,873 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828034</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136828042</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93423</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>412211</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6967712</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828042</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828040</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92574</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412393</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967794</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828040</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>412354</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967463</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828036</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828041</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412385</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828041</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>412209</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967343</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828044</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>412049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967512</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828044</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828045</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967185</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828045</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136828043</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412180</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967642</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828043</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92574</v>
+        <v>92576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92576</v>
+        <v>92578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92578</v>
+        <v>92579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92579</v>
+        <v>92585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135784660</v>
+        <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412209</v>
+        <v>412178</v>
       </c>
       <c r="R2" t="n">
-        <v>6967343</v>
+        <v>6967169</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +765,873 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828034</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136828042</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93438</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>412211</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6967712</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828042</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828040</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92589</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412393</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967794</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828040</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>412354</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967463</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828036</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828041</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80604</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412385</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828041</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>412209</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967343</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828044</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>412049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967512</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828044</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828045</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967185</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828045</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136828043</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93457</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412180</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967642</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828043</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135784660</v>
+        <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412209</v>
+        <v>412178</v>
       </c>
       <c r="R2" t="n">
-        <v>6967343</v>
+        <v>6967169</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +765,873 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828034</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136828042</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>412211</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6967712</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828042</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828040</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92591</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412393</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6967794</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828040</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80107</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>412354</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6967463</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828036</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828041</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80607</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412385</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828041</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>412209</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967343</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135784660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828044</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>412049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967512</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828044</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828045</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967185</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828045</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136828043</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93459</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412180</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967642</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828043</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92591</v>
+        <v>92604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136828044</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136828045</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92604</v>
+        <v>92606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136828044</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136828045</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -1326,11 +1326,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>
@@ -1438,11 +1434,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92606</v>
+        <v>92609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92609</v>
+        <v>92619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136828044</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136828045</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92619</v>
+        <v>92620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136828044</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136828045</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92623</v>
+        <v>92625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92625</v>
+        <v>92630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>136828044</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136828045</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 48508-2025 artfynd.xlsx
+++ b/artfynd/A 48508-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828034</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828042</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828040</v>
       </c>
       <c r="B4" t="n">
-        <v>92630</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828036</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828041</v>
       </c>
       <c r="B6" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136828043</v>
       </c>
       <c r="B10" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
